--- a/src/nodes/HPC/compressor_stage_parameters.xlsx
+++ b/src/nodes/HPC/compressor_stage_parameters.xlsx
@@ -653,10 +653,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="D3">
         <v>54.297485041069478</v>
@@ -665,16 +665,16 @@
         <v>22.571774167703115</v>
       </c>
       <c r="F3">
-        <v>30.517471086439947</v>
+        <v>26.2592193069367</v>
       </c>
       <c r="G3">
-        <v>11.591247429156738</v>
+        <v>8.1628503022230561</v>
       </c>
       <c r="H3">
-        <v>1.948065575885471</v>
+        <v>2.6693735071101408</v>
       </c>
       <c r="I3">
-        <v>-0.13172022561483532</v>
+        <v>1.9129572796269321</v>
       </c>
       <c r="J3">
         <v>0.29445421736099869</v>
@@ -683,34 +683,34 @@
         <v>0.28009052758785513</v>
       </c>
       <c r="L3">
-        <v>41.01459016284155</v>
+        <v>39.283385728623891</v>
       </c>
       <c r="M3">
-        <v>48.186033315664957</v>
+        <v>43.856761854789809</v>
       </c>
       <c r="N3">
-        <v>9.05400164143819</v>
+        <v>8.0441051384452</v>
       </c>
       <c r="O3">
-        <v>9.67167820238767</v>
+        <v>7.3870842467542888</v>
       </c>
       <c r="P3">
-        <v>20.507295081420775</v>
+        <v>19.641692864311945</v>
       </c>
       <c r="Q3">
-        <v>24.093016657832479</v>
+        <v>21.928380927394905</v>
       </c>
       <c r="R3">
-        <v>46.319597879518092</v>
+        <v>46.175303593633934</v>
       </c>
       <c r="S3">
-        <v>51.224258424051115</v>
+        <v>51.104300198855306</v>
       </c>
       <c r="T3">
-        <v>77.495512861590029</v>
+        <v>80.76689835938538</v>
       </c>
       <c r="U3">
-        <v>27.646634727856021</v>
+        <v>30.220826668455686</v>
       </c>
       <c r="V3">
         <v>1.0756736094709218</v>
@@ -719,25 +719,25 @@
         <v>0.84810804070334256</v>
       </c>
       <c r="X3">
-        <v>0.66546019160404546</v>
+        <v>0.6403577856097481</v>
       </c>
       <c r="Y3">
-        <v>0.75281277285546</v>
+        <v>0.69909122023701264</v>
       </c>
       <c r="Z3">
-        <v>0.14724649883798194</v>
+        <v>0.15704343857009359</v>
       </c>
       <c r="AA3">
-        <v>0.20080733843304355</v>
+        <v>0.23924907047034991</v>
       </c>
       <c r="AB3">
-        <v>9.97763019044093</v>
+        <v>9.2635311578758817</v>
       </c>
       <c r="AC3">
-        <v>6.1139824040777091</v>
+        <v>4.9438708689971316</v>
       </c>
       <c r="AD3">
-        <v>77.090928405576989</v>
+        <v>73.970532197398981</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -745,10 +745,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C4">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="D4">
         <v>48.942470423976722</v>
@@ -757,16 +757,16 @@
         <v>22.380635216702814</v>
       </c>
       <c r="F4">
-        <v>28.913192950156478</v>
+        <v>20.797208964147643</v>
       </c>
       <c r="G4">
-        <v>12.331180085684393</v>
+        <v>7.0259049325411063</v>
       </c>
       <c r="H4">
-        <v>1.7318458660332641</v>
+        <v>3.3832979113145378</v>
       </c>
       <c r="I4">
-        <v>-0.46259257808481952</v>
+        <v>2.9636130262184812</v>
       </c>
       <c r="J4">
         <v>0.31049376478890489</v>
@@ -775,34 +775,34 @@
         <v>0.275657180010517</v>
       </c>
       <c r="L4">
-        <v>35.834635444899185</v>
+        <v>32.135588463236118</v>
       </c>
       <c r="M4">
-        <v>53.219271769364866</v>
+        <v>46.009811360115329</v>
       </c>
       <c r="N4">
-        <v>8.5518673854548819</v>
+        <v>6.5042724490730839</v>
       </c>
       <c r="O4">
-        <v>10.889410061919607</v>
+        <v>7.1061552569733752</v>
       </c>
       <c r="P4">
-        <v>17.917317722449592</v>
+        <v>16.067794231618059</v>
       </c>
       <c r="Q4">
-        <v>26.609635884682433</v>
+        <v>23.004905680057664</v>
       </c>
       <c r="R4">
-        <v>40.387667268552853</v>
+        <v>40.189595823002591</v>
       </c>
       <c r="S4">
-        <v>48.719709163783882</v>
+        <v>48.541184563462416</v>
       </c>
       <c r="T4">
-        <v>79.543944832451842</v>
+        <v>88.415768139957649</v>
       </c>
       <c r="U4">
-        <v>24.983436710221362</v>
+        <v>28.633656507601188</v>
       </c>
       <c r="V4">
         <v>0.97500701780570942</v>
@@ -811,25 +811,25 @@
         <v>0.964396707220587</v>
       </c>
       <c r="X4">
-        <v>0.73758130252758458</v>
+        <v>0.68427122939144347</v>
       </c>
       <c r="Y4">
-        <v>0.80980452956563465</v>
+        <v>0.718830035771332</v>
       </c>
       <c r="Z4">
-        <v>0.19726203417069341</v>
+        <v>0.23000715035092925</v>
       </c>
       <c r="AA4">
-        <v>0.22006885683913816</v>
+        <v>0.289175115670015</v>
       </c>
       <c r="AB4">
-        <v>7.4015687547528675</v>
+        <v>6.1010938250357327</v>
       </c>
       <c r="AC4">
-        <v>6.5036754452354124</v>
+        <v>4.6134981920320595</v>
       </c>
       <c r="AD4">
-        <v>74.021361100695813</v>
+        <v>67.950466871140918</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -837,10 +837,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>266</v>
       </c>
       <c r="D5">
         <v>43.377606503792478</v>
@@ -849,16 +849,16 @@
         <v>21.369715574904451</v>
       </c>
       <c r="F5">
-        <v>25.950659952066804</v>
+        <v>15.439000224647343</v>
       </c>
       <c r="G5">
-        <v>12.196810177471399</v>
+        <v>4.5852669840118043</v>
       </c>
       <c r="H5">
-        <v>1.6788538888716902</v>
+        <v>4.5240310046992231</v>
       </c>
       <c r="I5">
-        <v>-0.61981467614044106</v>
+        <v>6.6512929614664262</v>
       </c>
       <c r="J5">
         <v>0.31871380347796441</v>
@@ -867,34 +867,34 @@
         <v>0.27566102546592752</v>
       </c>
       <c r="L5">
-        <v>33.990571530178464</v>
+        <v>28.111378097864076</v>
       </c>
       <c r="M5">
-        <v>60.796260580322837</v>
+        <v>46.845662296591264</v>
       </c>
       <c r="N5">
-        <v>8.3791651686264235</v>
+        <v>5.3451488521395651</v>
       </c>
       <c r="O5">
-        <v>12.66123287267769</v>
+        <v>5.9817422265529814</v>
       </c>
       <c r="P5">
-        <v>16.995285765089232</v>
+        <v>14.055689048932038</v>
       </c>
       <c r="Q5">
-        <v>30.398130290161419</v>
+        <v>23.422831148295632</v>
       </c>
       <c r="R5">
-        <v>37.026977664555005</v>
+        <v>36.93255806422534</v>
       </c>
       <c r="S5">
-        <v>50.913836026527832</v>
+        <v>51.20964452226891</v>
       </c>
       <c r="T5">
-        <v>74.202262001225151</v>
+        <v>89.303996522368166</v>
       </c>
       <c r="U5">
-        <v>21.116085299655634</v>
+        <v>26.879228117755908</v>
       </c>
       <c r="V5">
         <v>0.96374248262138207</v>
@@ -903,25 +903,25 @@
         <v>0.96371207021506655</v>
       </c>
       <c r="X5">
-        <v>0.77074687305321765</v>
+        <v>0.691696596891747</v>
       </c>
       <c r="Y5">
-        <v>0.84740311128582346</v>
+        <v>0.70734444015676945</v>
       </c>
       <c r="Z5">
-        <v>0.23125801629227011</v>
+        <v>0.30052345967652705</v>
       </c>
       <c r="AA5">
-        <v>0.23814985309711559</v>
+        <v>0.4073750325427028</v>
       </c>
       <c r="AB5">
-        <v>6.602370189325832</v>
+        <v>4.6246584264003765</v>
       </c>
       <c r="AC5">
-        <v>6.162668626890575</v>
+        <v>2.9811247683434852</v>
       </c>
       <c r="AD5">
-        <v>71.319953205216649</v>
+        <v>57.822408515769489</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -929,10 +929,10 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>272</v>
       </c>
       <c r="D6">
         <v>39.63000149255199</v>
@@ -941,16 +941,16 @@
         <v>20.714787403326294</v>
       </c>
       <c r="F6">
-        <v>24.891449341778365</v>
+        <v>14.019322043070574</v>
       </c>
       <c r="G6">
-        <v>12.196810177471399</v>
+        <v>4.4841213887762494</v>
       </c>
       <c r="H6">
-        <v>1.4802826412799623</v>
+        <v>4.5670324447215656</v>
       </c>
       <c r="I6">
-        <v>-0.75405636762545469</v>
+        <v>6.5489666800587631</v>
       </c>
       <c r="J6">
         <v>0.32778169831457576</v>
@@ -959,34 +959,34 @@
         <v>0.27412176389747123</v>
       </c>
       <c r="L6">
-        <v>30.616266300082181</v>
+        <v>24.316886827746938</v>
       </c>
       <c r="M6">
-        <v>61.367502512080279</v>
+        <v>47.172640953169839</v>
       </c>
       <c r="N6">
-        <v>7.9533478235867374</v>
+        <v>4.7407181546930968</v>
       </c>
       <c r="O6">
-        <v>12.908175425458623</v>
+        <v>6.0163369142323928</v>
       </c>
       <c r="P6">
-        <v>15.30813315004109</v>
+        <v>12.158443413873469</v>
       </c>
       <c r="Q6">
-        <v>30.683751256040139</v>
+        <v>23.58632047658492</v>
       </c>
       <c r="R6">
-        <v>33.754365516257764</v>
+        <v>33.691425583531753</v>
       </c>
       <c r="S6">
-        <v>50.373108561472662</v>
+        <v>50.57870082970166</v>
       </c>
       <c r="T6">
-        <v>75.053987586974245</v>
+        <v>94.081254514469</v>
       </c>
       <c r="U6">
-        <v>20.296713730427264</v>
+        <v>25.885056270681748</v>
       </c>
       <c r="V6">
         <v>0.96608699365910289</v>
@@ -995,25 +995,25 @@
         <v>0.96586889811156607</v>
       </c>
       <c r="X6">
-        <v>0.77016681354912508</v>
+        <v>0.6832795097856349</v>
       </c>
       <c r="Y6">
-        <v>0.8715948165329217</v>
+        <v>0.72260829653754566</v>
       </c>
       <c r="Z6">
-        <v>0.23909358296810868</v>
+        <v>0.31966518769382235</v>
       </c>
       <c r="AA6">
-        <v>0.24667029718018022</v>
+        <v>0.42225000859463269</v>
       </c>
       <c r="AB6">
-        <v>6.6250055029871922</v>
+        <v>4.4025650251501149</v>
       </c>
       <c r="AC6">
-        <v>6.0379233413273736</v>
+        <v>2.8880976308410578</v>
       </c>
       <c r="AD6">
-        <v>70.398843303169173</v>
+        <v>56.044040986101336</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1021,10 +1021,10 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="C7">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="D7">
         <v>36.893867620176927</v>
@@ -1033,16 +1033,16 @@
         <v>20.639837056997745</v>
       </c>
       <c r="F7">
-        <v>23.915314073473333</v>
+        <v>13.114849653195053</v>
       </c>
       <c r="G7">
-        <v>12.445724670889183</v>
+        <v>3.7185396882534754</v>
       </c>
       <c r="H7">
-        <v>1.3567199563876209</v>
+        <v>4.53284227341272</v>
       </c>
       <c r="I7">
-        <v>-0.85403068065719678</v>
+        <v>8.8763054769840757</v>
       </c>
       <c r="J7">
         <v>0.33412118043936573</v>
@@ -1051,34 +1051,34 @@
         <v>0.27655416352673634</v>
       </c>
       <c r="L7">
-        <v>28.5737090813739</v>
+        <v>22.116920319097368</v>
       </c>
       <c r="M7">
-        <v>63.58815040038133</v>
+        <v>45.5488993122672</v>
       </c>
       <c r="N7">
-        <v>7.6865521423255858</v>
+        <v>4.4058856970741536</v>
       </c>
       <c r="O7">
-        <v>13.655680789220039</v>
+        <v>5.3467658587471867</v>
       </c>
       <c r="P7">
-        <v>14.286854540686949</v>
+        <v>11.058460159548684</v>
       </c>
       <c r="Q7">
-        <v>31.794075200190665</v>
+        <v>22.7744496561336</v>
       </c>
       <c r="R7">
-        <v>31.339107381955792</v>
+        <v>31.286835317842623</v>
       </c>
       <c r="S7">
-        <v>50.497106579172339</v>
+        <v>51.207817192756551</v>
       </c>
       <c r="T7">
-        <v>74.751526572569091</v>
+        <v>96.172714775612761</v>
       </c>
       <c r="U7">
-        <v>19.587297650154337</v>
+        <v>26.659260593176377</v>
       </c>
       <c r="V7">
         <v>0.96734921344687119</v>
@@ -1087,25 +1087,25 @@
         <v>0.96700424992385381</v>
       </c>
       <c r="X7">
-        <v>0.77759117451196991</v>
+        <v>0.68581140167037291</v>
       </c>
       <c r="Y7">
-        <v>0.88973642850968937</v>
+        <v>0.71995779547982108</v>
       </c>
       <c r="Z7">
-        <v>0.25363033580587435</v>
+        <v>0.34309863172683275</v>
       </c>
       <c r="AA7">
-        <v>0.25624039936544268</v>
+        <v>0.50743275397283993</v>
       </c>
       <c r="AB7">
-        <v>6.4775297686540441</v>
+        <v>4.1626371280867822</v>
       </c>
       <c r="AC7">
-        <v>5.913769328323494</v>
+        <v>2.1865861591753153</v>
       </c>
       <c r="AD7">
-        <v>69.079422607917152</v>
+        <v>50.825959883217173</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1113,10 +1113,10 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C8">
-        <v>96</v>
+        <v>536</v>
       </c>
       <c r="D8">
         <v>34.798134742361746</v>
@@ -1125,16 +1125,16 @@
         <v>21.024897452414422</v>
       </c>
       <c r="F8">
-        <v>23.012849391455472</v>
+        <v>13.114849653195053</v>
       </c>
       <c r="G8">
-        <v>12.705010601532708</v>
+        <v>2.2755242868416792</v>
       </c>
       <c r="H8">
-        <v>1.2802940164465337</v>
+        <v>4.1333461043307107</v>
       </c>
       <c r="I8">
-        <v>-0.86287290270383177</v>
+        <v>18.098959626570274</v>
       </c>
       <c r="J8">
         <v>0.34094404379113646</v>
@@ -1143,34 +1143,34 @@
         <v>0.29006141321928208</v>
       </c>
       <c r="L8">
-        <v>25.64054190081821</v>
+        <v>19.828645651597931</v>
       </c>
       <c r="M8">
-        <v>63.216481385004286</v>
+        <v>33.165327313815546</v>
       </c>
       <c r="N8">
-        <v>7.1091474550619864</v>
+        <v>4.15030329372588</v>
       </c>
       <c r="O8">
-        <v>14.254134446800613</v>
+        <v>3.1648129048859692</v>
       </c>
       <c r="P8">
-        <v>12.820270950409105</v>
+        <v>9.9143228257989655</v>
       </c>
       <c r="Q8">
-        <v>31.608240692502143</v>
+        <v>16.582663656907773</v>
       </c>
       <c r="R8">
-        <v>28.816854609084672</v>
+        <v>28.763958572358707</v>
       </c>
       <c r="S8">
-        <v>49.636125703154086</v>
+        <v>53.572381196833817</v>
       </c>
       <c r="T8">
-        <v>78.411798571405285</v>
+        <v>101.05434412334003</v>
       </c>
       <c r="U8">
-        <v>20.057775614356856</v>
+        <v>36.834296000782373</v>
       </c>
       <c r="V8">
         <v>0.96841018460180273</v>
@@ -1179,25 +1179,25 @@
         <v>0.96795122424828028</v>
       </c>
       <c r="X8">
-        <v>0.76755694143931752</v>
+        <v>0.68085580463494155</v>
       </c>
       <c r="Y8">
-        <v>0.86915022706193834</v>
+        <v>0.679414839309151</v>
       </c>
       <c r="Z8">
-        <v>0.2612409546814255</v>
+        <v>0.34523041269551319</v>
       </c>
       <c r="AA8">
-        <v>0.2554450893847684</v>
+        <v>0.78325455367633379</v>
       </c>
       <c r="AB8">
-        <v>6.4620634869941886</v>
+        <v>4.25558055906969</v>
       </c>
       <c r="AC8">
-        <v>6.0141165940353574</v>
+        <v>0.788253393081707</v>
       </c>
       <c r="AD8">
-        <v>68.32660628776064</v>
+        <v>37.73808670003482</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -1205,10 +1205,10 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C9">
-        <v>90</v>
+        <v>428</v>
       </c>
       <c r="D9">
         <v>33.420203587904915</v>
@@ -1217,16 +1217,16 @@
         <v>22.15977275314977</v>
       </c>
       <c r="F9">
-        <v>20.672559622832882</v>
+        <v>17.676536489088985</v>
       </c>
       <c r="G9">
-        <v>13.552011308301553</v>
+        <v>2.8497220040821025</v>
       </c>
       <c r="H9">
-        <v>1.5416141249137132</v>
+        <v>2.2266334681194282</v>
       </c>
       <c r="I9">
-        <v>-0.91208783533567428</v>
+        <v>14.44029340529257</v>
       </c>
       <c r="J9">
         <v>0.35028221394354575</v>
@@ -1235,34 +1235,34 @@
         <v>0.30032922063489065</v>
       </c>
       <c r="L9">
-        <v>19.440730032156658</v>
+        <v>17.980412816715507</v>
       </c>
       <c r="M9">
-        <v>54.158366451788346</v>
+        <v>29.234705273703522</v>
       </c>
       <c r="N9">
-        <v>5.35578625516145</v>
+        <v>4.58048838292601</v>
       </c>
       <c r="O9">
-        <v>12.719861193349113</v>
+        <v>3.1485812558925348</v>
       </c>
       <c r="P9">
-        <v>9.720365016078329</v>
+        <v>8.9902064083577535</v>
       </c>
       <c r="Q9">
-        <v>27.079183225894173</v>
+        <v>14.617352636851761</v>
       </c>
       <c r="R9">
-        <v>25.494314267310259</v>
+        <v>25.449175002795396</v>
       </c>
       <c r="S9">
-        <v>45.073409844823281</v>
+        <v>47.963960496409108</v>
       </c>
       <c r="T9">
-        <v>98.970203216003085</v>
+        <v>106.93395002903648</v>
       </c>
       <c r="U9">
-        <v>24.339552813027904</v>
+        <v>43.904659173702626</v>
       </c>
       <c r="V9">
         <v>0.9697562157220061</v>
@@ -1271,25 +1271,25 @@
         <v>0.96918262734228977</v>
       </c>
       <c r="X9">
-        <v>0.6924587155179377</v>
+        <v>0.66762673127874572</v>
       </c>
       <c r="Y9">
-        <v>0.8374909011503302</v>
+        <v>0.66246324367271159</v>
       </c>
       <c r="Z9">
-        <v>0.2489691512027318</v>
+        <v>0.26782222074708595</v>
       </c>
       <c r="AA9">
-        <v>0.24321853221458464</v>
+        <v>0.659181212746055</v>
       </c>
       <c r="AB9">
-        <v>6.7256304576492862</v>
+        <v>6.0539619507127558</v>
       </c>
       <c r="AC9">
-        <v>6.3162702315701136</v>
+        <v>1.1938775052918125</v>
       </c>
       <c r="AD9">
-        <v>68.4314374574077</v>
+        <v>48.005741179686424</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -1297,10 +1297,10 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="D10">
         <v>32.838799934799347</v>
@@ -1309,16 +1309,16 @@
         <v>24.186566983792741</v>
       </c>
       <c r="F10">
-        <v>22.176018504493456</v>
+        <v>23.012849391455472</v>
       </c>
       <c r="G10">
-        <v>14.874158753013901</v>
+        <v>3.3692845794119886</v>
       </c>
       <c r="H10">
-        <v>1.202062199324162</v>
+        <v>1.067441755712375</v>
       </c>
       <c r="I10">
-        <v>-0.93480085404966218</v>
+        <v>12.946366961390517</v>
       </c>
       <c r="J10">
         <v>0.35675656072260425</v>
@@ -1327,34 +1327,34 @@
         <v>0.30831341411958829</v>
       </c>
       <c r="L10">
-        <v>16.595229945808928</v>
+        <v>16.916848850947353</v>
       </c>
       <c r="M10">
-        <v>47.610341823126191</v>
+        <v>25.107065500424561</v>
       </c>
       <c r="N10">
-        <v>4.8652301753372624</v>
+        <v>5.0522286368639</v>
       </c>
       <c r="O10">
-        <v>11.511258628114184</v>
+        <v>2.8891501208527353</v>
       </c>
       <c r="P10">
-        <v>8.2976149729044639</v>
+        <v>8.4584244254736767</v>
       </c>
       <c r="Q10">
-        <v>23.805170911563096</v>
+        <v>12.55353275021228</v>
       </c>
       <c r="R10">
-        <v>23.189334841130684</v>
+        <v>23.215523850088108</v>
       </c>
       <c r="S10">
-        <v>41.522471243368521</v>
+        <v>44.152000897457889</v>
       </c>
       <c r="T10">
-        <v>113.77472054083549</v>
+        <v>111.62695531608848</v>
       </c>
       <c r="U10">
-        <v>29.96146800490078</v>
+        <v>55.639241724307993</v>
       </c>
       <c r="V10">
         <v>0.97020586529407171</v>
@@ -1363,25 +1363,25 @@
         <v>0.96953741227665191</v>
       </c>
       <c r="X10">
-        <v>0.66096992472647331</v>
+        <v>0.66751270705038956</v>
       </c>
       <c r="Y10">
-        <v>0.81381263548375171</v>
+        <v>0.64852276043169277</v>
       </c>
       <c r="Z10">
-        <v>0.22785245882826363</v>
+        <v>0.22450332649505425</v>
       </c>
       <c r="AA10">
-        <v>0.23725903325510797</v>
+        <v>0.61171517315693436</v>
       </c>
       <c r="AB10">
-        <v>7.48248728422799</v>
+        <v>7.6391705246002664</v>
       </c>
       <c r="AC10">
-        <v>6.4950804040815395</v>
+        <v>1.3707832671762759</v>
       </c>
       <c r="AD10">
-        <v>69.314455201798211</v>
+        <v>52.640725374590438</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -1389,10 +1389,10 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C11">
-        <v>74</v>
+        <v>242</v>
       </c>
       <c r="D11">
         <v>32.497043688956481</v>
@@ -1401,16 +1401,16 @@
         <v>26.45438493799168</v>
       </c>
       <c r="F11">
-        <v>22.176018504493456</v>
+        <v>24.891449341778365</v>
       </c>
       <c r="G11">
-        <v>16.482175915501891</v>
+        <v>5.040004205566694</v>
       </c>
       <c r="H11">
-        <v>1.1635345161679616</v>
+        <v>0.76387620531327527</v>
       </c>
       <c r="I11">
-        <v>-0.98742528389248074</v>
+        <v>8.1222038013245914</v>
       </c>
       <c r="J11">
         <v>0.36055700223691628</v>
@@ -1419,34 +1419,34 @@
         <v>0.30705666658165642</v>
       </c>
       <c r="L11">
-        <v>14.901645956076186</v>
+        <v>15.871123908045632</v>
       </c>
       <c r="M11">
-        <v>44.712416137677195</v>
+        <v>28.598839568502967</v>
       </c>
       <c r="N11">
-        <v>4.438416313696238</v>
+        <v>5.0082359548109956</v>
       </c>
       <c r="O11">
-        <v>10.836901044563234</v>
+        <v>3.8329535606060756</v>
       </c>
       <c r="P11">
-        <v>7.4508229780380928</v>
+        <v>7.9355619540228162</v>
       </c>
       <c r="Q11">
-        <v>22.356208068838598</v>
+        <v>14.299419784251484</v>
       </c>
       <c r="R11">
-        <v>21.709092217200013</v>
+        <v>21.794172882330052</v>
       </c>
       <c r="S11">
-        <v>39.952359684896429</v>
+        <v>41.005200485526387</v>
       </c>
       <c r="T11">
-        <v>125.30170438203658</v>
+        <v>117.692336459628</v>
       </c>
       <c r="U11">
-        <v>34.775124898419243</v>
+        <v>53.553728177473772</v>
       </c>
       <c r="V11">
         <v>0.99360462702951247</v>
@@ -1455,25 +1455,25 @@
         <v>0.99366900342747122</v>
       </c>
       <c r="X11">
-        <v>0.62721950095530388</v>
+        <v>0.6474847120459436</v>
       </c>
       <c r="Y11">
-        <v>0.81193561441103057</v>
+        <v>0.66147906098927722</v>
       </c>
       <c r="Z11">
-        <v>0.21513033580021007</v>
+        <v>0.2055443906217084</v>
       </c>
       <c r="AA11">
-        <v>0.23079362410346019</v>
+        <v>0.46341392933209929</v>
       </c>
       <c r="AB11">
-        <v>8.3667009966966361</v>
+        <v>8.9074683079311878</v>
       </c>
       <c r="AC11">
-        <v>6.8289242970233994</v>
+        <v>2.45592678925117</v>
       </c>
       <c r="AD11">
-        <v>70.492859300527712</v>
+        <v>61.064068390681335</v>
       </c>
     </row>
   </sheetData>
@@ -1795,10 +1795,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="D3">
         <v>63.23176353246707</v>
@@ -1807,16 +1807,16 @@
         <v>25.047794512619152</v>
       </c>
       <c r="F3">
-        <v>39.1944404289641</v>
+        <v>33.72544874120166</v>
       </c>
       <c r="G3">
-        <v>14.501942958716716</v>
+        <v>10.212635886420223</v>
       </c>
       <c r="H3">
-        <v>1.5332099935874932</v>
+        <v>2.1872440466016818</v>
       </c>
       <c r="I3">
-        <v>-0.68199333980216437</v>
+        <v>1.1315694574809265</v>
       </c>
       <c r="J3">
         <v>0.35493169719716439</v>
@@ -1825,34 +1825,34 @@
         <v>0.27174229954603668</v>
       </c>
       <c r="L3">
-        <v>12.093857166366449</v>
+        <v>10.880731479890292</v>
       </c>
       <c r="M3">
-        <v>47.825937691214463</v>
+        <v>43.707419448475491</v>
       </c>
       <c r="N3">
-        <v>3.3795136731769015</v>
+        <v>2.8204220397149316</v>
       </c>
       <c r="O3">
-        <v>9.8889251635091977</v>
+        <v>7.583969718053301</v>
       </c>
       <c r="P3">
-        <v>6.0469285831832247</v>
+        <v>5.4403657399451459</v>
       </c>
       <c r="Q3">
-        <v>23.912968845607232</v>
+        <v>21.853709724237746</v>
       </c>
       <c r="R3">
-        <v>24.8667364914115</v>
+        <v>24.91420770118761</v>
       </c>
       <c r="S3">
-        <v>52.171231473253314</v>
+        <v>51.925535149166912</v>
       </c>
       <c r="T3">
-        <v>300.12323468108303</v>
+        <v>333.46681826009012</v>
       </c>
       <c r="U3">
-        <v>30.896615464369912</v>
+        <v>33.644860876695674</v>
       </c>
       <c r="V3">
         <v>0.97396676334521359</v>
@@ -1861,25 +1861,25 @@
         <v>0.96909397099996952</v>
       </c>
       <c r="X3">
-        <v>0.49780507434741017</v>
+        <v>0.48052084106559778</v>
       </c>
       <c r="Y3">
-        <v>0.69970264939757165</v>
+        <v>0.6400817064007065</v>
       </c>
       <c r="Z3">
-        <v>0.13511334013063928</v>
+        <v>0.14748951904564617</v>
       </c>
       <c r="AA3">
-        <v>0.14519201071703858</v>
+        <v>0.16848261319618732</v>
       </c>
       <c r="AB3">
-        <v>10.079340372412757</v>
+        <v>9.020358785000548</v>
       </c>
       <c r="AC3">
-        <v>8.9736875674258467</v>
+        <v>7.5826479378724319</v>
       </c>
       <c r="AD3">
-        <v>77.74153002426965</v>
+        <v>75.294207023781624</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -1887,10 +1887,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C4">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="D4">
         <v>56.879953285173634</v>
@@ -1899,16 +1899,16 @@
         <v>24.800427364727152</v>
       </c>
       <c r="F4">
-        <v>35.370592582235894</v>
+        <v>25.442005190731084</v>
       </c>
       <c r="G4">
-        <v>14.797900978282362</v>
+        <v>8.431362185300415</v>
       </c>
       <c r="H4">
-        <v>1.5202855771308417</v>
+        <v>3.0891775096697049</v>
       </c>
       <c r="I4">
-        <v>-0.81014439123415938</v>
+        <v>2.3536241296706595</v>
       </c>
       <c r="J4">
         <v>0.35636025268174581</v>
@@ -1917,34 +1917,34 @@
         <v>0.26899173271182941</v>
       </c>
       <c r="L4">
-        <v>12.793205712013659</v>
+        <v>10.016485505263553</v>
       </c>
       <c r="M4">
-        <v>53.042444700922459</v>
+        <v>46.085436144266026</v>
       </c>
       <c r="N4">
-        <v>3.5950935335907483</v>
+        <v>2.3872652593795056</v>
       </c>
       <c r="O4">
-        <v>11.021302962758517</v>
+        <v>7.2280629270069046</v>
       </c>
       <c r="P4">
-        <v>6.3966028560068295</v>
+        <v>5.0082427526317765</v>
       </c>
       <c r="Q4">
-        <v>26.52122235046123</v>
+        <v>23.042718072133013</v>
       </c>
       <c r="R4">
-        <v>24.018364336711024</v>
+        <v>24.198896165874832</v>
       </c>
       <c r="S4">
-        <v>52.452627273989137</v>
+        <v>52.137891516565738</v>
       </c>
       <c r="T4">
-        <v>255.27308182560111</v>
+        <v>325.77644515872805</v>
       </c>
       <c r="U4">
-        <v>27.770214909147558</v>
+        <v>31.680288529333509</v>
       </c>
       <c r="V4">
         <v>0.97044453170056677</v>
@@ -1953,25 +1953,25 @@
         <v>0.97014334544856362</v>
       </c>
       <c r="X4">
-        <v>0.53668468322111251</v>
+        <v>0.49929366625675559</v>
       </c>
       <c r="Y4">
-        <v>0.757239989051824</v>
+        <v>0.66244994495928644</v>
       </c>
       <c r="Z4">
-        <v>0.15880193612625143</v>
+        <v>0.19287813487280259</v>
       </c>
       <c r="AA4">
-        <v>0.16846840230800342</v>
+        <v>0.21622918883319348</v>
       </c>
       <c r="AB4">
-        <v>9.1809236632268441</v>
+        <v>7.0833309665251232</v>
       </c>
       <c r="AC4">
-        <v>8.0667376080409081</v>
+        <v>6.0278311797179693</v>
       </c>
       <c r="AD4">
-        <v>75.359146976634122</v>
+        <v>69.624567672697424</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -1979,10 +1979,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>266</v>
       </c>
       <c r="D5">
         <v>50.34304045521165</v>
@@ -1991,16 +1991,16 @@
         <v>23.6573681894641</v>
       </c>
       <c r="F5">
-        <v>30.696642378540549</v>
+        <v>18.262559389764633</v>
       </c>
       <c r="G5">
-        <v>14.281844369692001</v>
+        <v>5.3691144246962414</v>
       </c>
       <c r="H5">
-        <v>1.6000445451328527</v>
+        <v>4.39156423543607</v>
       </c>
       <c r="I5">
-        <v>-0.85883875060488946</v>
+        <v>6.0154889233909952</v>
       </c>
       <c r="J5">
         <v>0.35696383987662217</v>
@@ -2009,34 +2009,34 @@
         <v>0.269732101325685</v>
       </c>
       <c r="L5">
-        <v>13.743086464465002</v>
+        <v>9.0710816283911537</v>
       </c>
       <c r="M5">
-        <v>60.444626376187209</v>
+        <v>46.933473358662489</v>
       </c>
       <c r="N5">
-        <v>3.8307536169540253</v>
+        <v>1.9502684711833955</v>
       </c>
       <c r="O5">
-        <v>12.667743666147183</v>
+        <v>6.0309183226183531</v>
       </c>
       <c r="P5">
-        <v>6.8715432322325007</v>
+        <v>4.5355408141955769</v>
       </c>
       <c r="Q5">
-        <v>30.222313188093604</v>
+        <v>23.466736679331245</v>
       </c>
       <c r="R5">
-        <v>23.47729044641045</v>
+        <v>23.932807718676745</v>
       </c>
       <c r="S5">
-        <v>53.899899899120754</v>
+        <v>54.018651064354287</v>
       </c>
       <c r="T5">
-        <v>210.3872435689153</v>
+        <v>318.31467788103913</v>
       </c>
       <c r="U5">
-        <v>23.499615718224831</v>
+        <v>29.704146289229076</v>
       </c>
       <c r="V5">
         <v>0.96374248262138207</v>
@@ -2045,25 +2045,25 @@
         <v>0.96371207021506655</v>
       </c>
       <c r="X5">
-        <v>0.58313977335209832</v>
+        <v>0.5256139463740539</v>
       </c>
       <c r="Y5">
-        <v>0.80541649468937715</v>
+        <v>0.6612948083177459</v>
       </c>
       <c r="Z5">
-        <v>0.19321079823250154</v>
+        <v>0.26432850475156111</v>
       </c>
       <c r="AA5">
-        <v>0.19418516943187317</v>
+        <v>0.32337998394597328</v>
       </c>
       <c r="AB5">
-        <v>7.9687960002039713</v>
+        <v>5.0631048950766937</v>
       </c>
       <c r="AC5">
-        <v>7.2152292413039669</v>
+        <v>3.8254972612497191</v>
       </c>
       <c r="AD5">
-        <v>72.0485187833624</v>
+        <v>59.590466802353468</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -2071,10 +2071,10 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>272</v>
       </c>
       <c r="D6">
         <v>45.952774375076565</v>
@@ -2083,16 +2083,16 @@
         <v>22.918082737302473</v>
       </c>
       <c r="F6">
-        <v>28.885944293540671</v>
+        <v>16.269095061879227</v>
       </c>
       <c r="G6">
-        <v>14.042866095996006</v>
+        <v>5.16281841764559</v>
       </c>
       <c r="H6">
-        <v>1.4770877756411349</v>
+        <v>4.5613599281791579</v>
       </c>
       <c r="I6">
-        <v>-0.91997769888352288</v>
+        <v>6.0976606590368192</v>
       </c>
       <c r="J6">
         <v>0.35928941511818391</v>
@@ -2101,34 +2101,34 @@
         <v>0.26892281189608769</v>
       </c>
       <c r="L6">
-        <v>13.515351095195689</v>
+        <v>8.3705653130060949</v>
       </c>
       <c r="M6">
-        <v>61.159696858571863</v>
+        <v>47.305529060045743</v>
       </c>
       <c r="N6">
-        <v>3.8499861854031789</v>
+        <v>1.7894725557516087</v>
       </c>
       <c r="O6">
-        <v>12.874539489358027</v>
+        <v>6.0380100487522439</v>
       </c>
       <c r="P6">
-        <v>6.7576755475978443</v>
+        <v>4.1852826565030474</v>
       </c>
       <c r="Q6">
-        <v>30.579848429285931</v>
+        <v>23.652764530022871</v>
       </c>
       <c r="R6">
-        <v>22.447603078713382</v>
+        <v>22.959482340156608</v>
       </c>
       <c r="S6">
-        <v>53.022348753726057</v>
+        <v>53.112903212383337</v>
       </c>
       <c r="T6">
-        <v>195.26049928613978</v>
+        <v>314.82257795678561</v>
       </c>
       <c r="U6">
-        <v>22.5244166771502</v>
+        <v>28.562433483124938</v>
       </c>
       <c r="V6">
         <v>0.96608699365910289</v>
@@ -2137,25 +2137,25 @@
         <v>0.96586889811156607</v>
       </c>
       <c r="X6">
-        <v>0.59345455442567863</v>
+        <v>0.52909128739694289</v>
       </c>
       <c r="Y6">
-        <v>0.8335670326635416</v>
+        <v>0.68193624107473472</v>
       </c>
       <c r="Z6">
-        <v>0.20266060739963873</v>
+        <v>0.28594777789068604</v>
       </c>
       <c r="AA6">
-        <v>0.20799154766034161</v>
+        <v>0.3484754419947747</v>
       </c>
       <c r="AB6">
-        <v>7.898097468702538</v>
+        <v>4.7257455814847606</v>
       </c>
       <c r="AC6">
-        <v>6.8703893957945512</v>
+        <v>3.5652374311082013</v>
       </c>
       <c r="AD6">
-        <v>70.960304805519627</v>
+        <v>57.017733461202</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -2163,10 +2163,10 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="C7">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="D7">
         <v>42.74921107749946</v>
@@ -2175,16 +2175,16 @@
         <v>22.823638732226122</v>
       </c>
       <c r="F7">
-        <v>27.339902962266155</v>
+        <v>14.992850011565311</v>
       </c>
       <c r="G7">
-        <v>14.137588733368196</v>
+        <v>4.2240356581404974</v>
       </c>
       <c r="H7">
-        <v>1.4090492691671992</v>
+        <v>4.6282663143637155</v>
       </c>
       <c r="I7">
-        <v>-0.964014945781258</v>
+        <v>8.5081948753443619</v>
       </c>
       <c r="J7">
         <v>0.36118596130262437</v>
@@ -2193,34 +2193,34 @@
         <v>0.27160424419147444</v>
       </c>
       <c r="L7">
-        <v>13.475738295298914</v>
+        <v>8.0958023117956035</v>
       </c>
       <c r="M7">
-        <v>63.378026175341439</v>
+        <v>45.69745445253411</v>
       </c>
       <c r="N7">
-        <v>3.8924035688128913</v>
+        <v>1.7316846305060971</v>
       </c>
       <c r="O7">
-        <v>13.547853486979673</v>
+        <v>5.3394915852979619</v>
       </c>
       <c r="P7">
-        <v>6.737869147649457</v>
+        <v>4.0479011558978018</v>
       </c>
       <c r="Q7">
-        <v>31.68901308767072</v>
+        <v>22.848727226267055</v>
       </c>
       <c r="R7">
-        <v>21.561553769851255</v>
+        <v>22.090802823296112</v>
       </c>
       <c r="S7">
-        <v>52.80114815841754</v>
+        <v>53.4330721181395</v>
       </c>
       <c r="T7">
-        <v>182.17955117983661</v>
+        <v>302.79743031545053</v>
       </c>
       <c r="U7">
-        <v>21.724033677990249</v>
+        <v>29.389223977384603</v>
       </c>
       <c r="V7">
         <v>0.96734921344687119</v>
@@ -2229,25 +2229,25 @@
         <v>0.96700424992385381</v>
       </c>
       <c r="X7">
-        <v>0.60978681585598249</v>
+        <v>0.540736888325397</v>
       </c>
       <c r="Y7">
-        <v>0.85546307750614736</v>
+        <v>0.684194266794358</v>
       </c>
       <c r="Z7">
-        <v>0.21862547679470271</v>
+        <v>0.31195570104182496</v>
       </c>
       <c r="AA7">
-        <v>0.22161919286109097</v>
+        <v>0.43108005667151872</v>
       </c>
       <c r="AB7">
-        <v>7.6106818526306643</v>
+        <v>4.3876409820864488</v>
       </c>
       <c r="AC7">
-        <v>6.5771647844949159</v>
+        <v>2.6930559649434773</v>
       </c>
       <c r="AD7">
-        <v>69.411106694397432</v>
+        <v>52.200260088280196</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -2255,10 +2255,10 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C8">
-        <v>96</v>
+        <v>536</v>
       </c>
       <c r="D8">
         <v>40.297215286655771</v>
@@ -2267,16 +2267,16 @@
         <v>23.239912814250307</v>
       </c>
       <c r="F8">
-        <v>25.993710093753474</v>
+        <v>14.813619730848755</v>
       </c>
       <c r="G8">
-        <v>14.279484808324225</v>
+        <v>2.5575196671625475</v>
       </c>
       <c r="H8">
-        <v>1.3756698390988404</v>
+        <v>4.3007036799281542</v>
       </c>
       <c r="I8">
-        <v>-0.9312410205614351</v>
+        <v>17.717237635198657</v>
       </c>
       <c r="J8">
         <v>0.36372844389870357</v>
@@ -2285,34 +2285,34 @@
         <v>0.28455095995724811</v>
       </c>
       <c r="L8">
-        <v>12.725294307590382</v>
+        <v>7.8038286116492213</v>
       </c>
       <c r="M8">
-        <v>63.159601215983749</v>
+        <v>33.594668598180121</v>
       </c>
       <c r="N8">
-        <v>3.7174207409762019</v>
+        <v>1.7209888858643572</v>
       </c>
       <c r="O8">
-        <v>14.08764685982268</v>
+        <v>3.1711928977791377</v>
       </c>
       <c r="P8">
-        <v>6.3626471537951907</v>
+        <v>3.9019143058246106</v>
       </c>
       <c r="Q8">
-        <v>31.579800607991874</v>
+        <v>16.79733429909006</v>
       </c>
       <c r="R8">
-        <v>20.490551637829231</v>
+        <v>20.954852630687963</v>
       </c>
       <c r="S8">
-        <v>51.761982847809122</v>
+        <v>55.6279951946674</v>
       </c>
       <c r="T8">
-        <v>181.81211264552331</v>
+        <v>296.09133000512566</v>
       </c>
       <c r="U8">
-        <v>22.188802583683966</v>
+        <v>40.209234565984389</v>
       </c>
       <c r="V8">
         <v>0.96841018460180273</v>
@@ -2321,25 +2321,25 @@
         <v>0.96795122424828028</v>
       </c>
       <c r="X8">
-        <v>0.6091648650799838</v>
+        <v>0.54326706535178615</v>
       </c>
       <c r="Y8">
-        <v>0.83907719738359765</v>
+        <v>0.64915048263912367</v>
       </c>
       <c r="Z8">
-        <v>0.22746427986745513</v>
+        <v>0.3158599938754339</v>
       </c>
       <c r="AA8">
-        <v>0.22372393300197743</v>
+        <v>0.67700269383739053</v>
       </c>
       <c r="AB8">
-        <v>7.4946438077383863</v>
+        <v>4.4617838647550565</v>
       </c>
       <c r="AC8">
-        <v>6.6001836488870449</v>
+        <v>1.1470698221359241</v>
       </c>
       <c r="AD8">
-        <v>68.446706919960619</v>
+        <v>42.6497528377628</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -2347,10 +2347,10 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C9">
-        <v>90</v>
+        <v>428</v>
       </c>
       <c r="D9">
         <v>38.684524434166242</v>
@@ -2359,16 +2359,16 @@
         <v>24.486831261256107</v>
       </c>
       <c r="F9">
-        <v>23.137726737399358</v>
+        <v>19.78443300734148</v>
       </c>
       <c r="G9">
-        <v>15.116751696300677</v>
+        <v>3.1787561978202357</v>
       </c>
       <c r="H9">
-        <v>1.6798104102030638</v>
+        <v>2.3882528526103632</v>
       </c>
       <c r="I9">
-        <v>-0.950381445497903</v>
+        <v>14.258186014743309</v>
       </c>
       <c r="J9">
         <v>0.36791292173916107</v>
@@ -2377,34 +2377,34 @@
         <v>0.29463813107501619</v>
       </c>
       <c r="L9">
-        <v>9.74985250726911</v>
+        <v>8.50497828897114</v>
       </c>
       <c r="M9">
-        <v>54.706308853722341</v>
+        <v>30.020063827306586</v>
       </c>
       <c r="N9">
-        <v>2.7741810438309162</v>
+        <v>2.2377492679402469</v>
       </c>
       <c r="O9">
-        <v>12.664536780336821</v>
+        <v>3.1868592141622871</v>
       </c>
       <c r="P9">
-        <v>4.8749262536345546</v>
+        <v>4.25248914448557</v>
       </c>
       <c r="Q9">
-        <v>27.35315442686117</v>
+        <v>15.010031913653293</v>
       </c>
       <c r="R9">
-        <v>18.942793920615834</v>
+        <v>19.028799253874151</v>
       </c>
       <c r="S9">
-        <v>47.3706178980547</v>
+        <v>50.236062845088043</v>
       </c>
       <c r="T9">
-        <v>227.60718438172285</v>
+        <v>260.84678258752035</v>
       </c>
       <c r="U9">
-        <v>26.646605535638024</v>
+        <v>47.274035205396942</v>
       </c>
       <c r="V9">
         <v>0.9697562157220061</v>
@@ -2413,25 +2413,25 @@
         <v>0.96918262734228977</v>
       </c>
       <c r="X9">
-        <v>0.55099721204848962</v>
+        <v>0.53210143865732829</v>
       </c>
       <c r="Y9">
-        <v>0.81011335991501732</v>
+        <v>0.63597553612563762</v>
       </c>
       <c r="Z9">
-        <v>0.21839975830880559</v>
+        <v>0.23864554283353975</v>
       </c>
       <c r="AA9">
-        <v>0.21441410778597378</v>
+        <v>0.57686303031595343</v>
       </c>
       <c r="AB9">
-        <v>7.5855392590745172</v>
+        <v>6.6419722715388829</v>
       </c>
       <c r="AC9">
-        <v>6.8802757159358627</v>
+        <v>1.5449294153022408</v>
       </c>
       <c r="AD9">
-        <v>68.115577154761283</v>
+        <v>52.419302485341433</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -2439,10 +2439,10 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="D10">
         <v>38.000009063776496</v>
@@ -2451,16 +2451,16 @@
         <v>26.720803528433414</v>
       </c>
       <c r="F10">
-        <v>24.66625118030095</v>
+        <v>25.597053111633063</v>
       </c>
       <c r="G10">
-        <v>16.506261483761978</v>
+        <v>3.7389874079239842</v>
       </c>
       <c r="H10">
-        <v>1.3514171434089057</v>
+        <v>1.2113656109213089</v>
       </c>
       <c r="I10">
-        <v>-0.95292920284826776</v>
+        <v>12.866336933767407</v>
       </c>
       <c r="J10">
         <v>0.37125983003512508</v>
@@ -2469,34 +2469,34 @@
         <v>0.30260564132925694</v>
       </c>
       <c r="L10">
-        <v>8.6539166343164453</v>
+        <v>8.92493747236424</v>
       </c>
       <c r="M10">
-        <v>48.486010173943207</v>
+        <v>26.088108186606043</v>
       </c>
       <c r="N10">
-        <v>2.588513256379092</v>
+        <v>2.7194825619392913</v>
       </c>
       <c r="O10">
-        <v>11.531692996783791</v>
+        <v>2.9530571460623007</v>
       </c>
       <c r="P10">
-        <v>4.3269583171582227</v>
+        <v>4.46246873618212</v>
       </c>
       <c r="Q10">
-        <v>24.243005086971603</v>
+        <v>13.044054093303021</v>
       </c>
       <c r="R10">
-        <v>17.631639921658348</v>
+        <v>17.627098808194653</v>
       </c>
       <c r="S10">
-        <v>43.868475540306683</v>
+        <v>46.488790683253768</v>
       </c>
       <c r="T10">
-        <v>251.82944989000939</v>
+        <v>244.19699407849708</v>
       </c>
       <c r="U10">
-        <v>32.538130783581131</v>
+        <v>59.195355296703084</v>
       </c>
       <c r="V10">
         <v>0.97020586529407171</v>
@@ -2505,25 +2505,25 @@
         <v>0.96953741227665191</v>
       </c>
       <c r="X10">
-        <v>0.52616036910006292</v>
+        <v>0.53114206900052663</v>
       </c>
       <c r="Y10">
-        <v>0.7889727021436832</v>
+        <v>0.62512519520657428</v>
       </c>
       <c r="Z10">
-        <v>0.19925113408858011</v>
+        <v>0.19548594483097129</v>
       </c>
       <c r="AA10">
-        <v>0.21043269318196223</v>
+        <v>0.54049399393958131</v>
       </c>
       <c r="AB10">
-        <v>8.3949687743180412</v>
+        <v>8.6287273456877838</v>
       </c>
       <c r="AC10">
-        <v>7.0294400814028162</v>
+        <v>1.7060646334380056</v>
       </c>
       <c r="AD10">
-        <v>69.062022729891638</v>
+        <v>57.113061558196463</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -2531,10 +2531,10 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C11">
-        <v>74</v>
+        <v>242</v>
       </c>
       <c r="D11">
         <v>37.592193165271631</v>
@@ -2543,16 +2543,16 @@
         <v>29.219539964669853</v>
       </c>
       <c r="F11">
-        <v>24.534488479045471</v>
+        <v>27.538711558112261</v>
       </c>
       <c r="G11">
-        <v>18.166546280898263</v>
+        <v>5.5550596065556661</v>
       </c>
       <c r="H11">
-        <v>1.3305458454308665</v>
+        <v>0.91266811683840821</v>
       </c>
       <c r="I11">
-        <v>-0.97893574363752622</v>
+        <v>8.1499668924286333</v>
       </c>
       <c r="J11">
         <v>0.37307197826329785</v>
@@ -2561,34 +2561,34 @@
         <v>0.30179176133933289</v>
       </c>
       <c r="L11">
-        <v>8.1226496116947757</v>
+        <v>8.9503926378631249</v>
       </c>
       <c r="M11">
-        <v>45.503728402456545</v>
+        <v>29.417689808647662</v>
       </c>
       <c r="N11">
-        <v>2.4481048908216416</v>
+        <v>2.8579701883975308</v>
       </c>
       <c r="O11">
-        <v>10.828139944923153</v>
+        <v>3.8710039871804325</v>
       </c>
       <c r="P11">
-        <v>4.0613248058473879</v>
+        <v>4.4751963189315624</v>
       </c>
       <c r="Q11">
-        <v>22.751864201228273</v>
+        <v>14.708844904323831</v>
       </c>
       <c r="R11">
-        <v>16.850790953325323</v>
+        <v>16.846784737817043</v>
       </c>
       <c r="S11">
-        <v>42.180395074028446</v>
+        <v>43.266278413190165</v>
       </c>
       <c r="T11">
-        <v>265.39107936859455</v>
+        <v>240.89061535080035</v>
       </c>
       <c r="U11">
-        <v>37.776628919433428</v>
+        <v>57.539787982716135</v>
       </c>
       <c r="V11">
         <v>0.99360462702951247</v>
@@ -2597,25 +2597,25 @@
         <v>0.99366900342747122</v>
       </c>
       <c r="X11">
-        <v>0.50363318993546136</v>
+        <v>0.51917219781922808</v>
       </c>
       <c r="Y11">
-        <v>0.78567801785778557</v>
+        <v>0.63753602589121983</v>
       </c>
       <c r="Z11">
-        <v>0.19130108251777533</v>
+        <v>0.18028560842999492</v>
       </c>
       <c r="AA11">
-        <v>0.20586641397560068</v>
+        <v>0.41313441965217385</v>
       </c>
       <c r="AB11">
-        <v>9.3527830117410513</v>
+        <v>10.165860976908002</v>
       </c>
       <c r="AC11">
-        <v>7.3491478300554451</v>
+        <v>2.8074593870141071</v>
       </c>
       <c r="AD11">
-        <v>70.249794071340659</v>
+        <v>63.858384485896615</v>
       </c>
     </row>
   </sheetData>
@@ -2937,10 +2937,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="D3">
         <v>70.586730553390339</v>
@@ -2949,16 +2949,16 @@
         <v>27.086129001243737</v>
       </c>
       <c r="F3">
-        <v>46.269234012210525</v>
+        <v>39.81306182446022</v>
       </c>
       <c r="G3">
-        <v>16.918175833023277</v>
+        <v>11.914208333114983</v>
       </c>
       <c r="H3">
-        <v>1.3139128548552581</v>
+        <v>1.932385209696651</v>
       </c>
       <c r="I3">
-        <v>-0.99748086487356125</v>
+        <v>0.68357717187954359</v>
       </c>
       <c r="J3">
         <v>0.3735636007525957</v>
@@ -2967,34 +2967,34 @@
         <v>0.2665848053335918</v>
       </c>
       <c r="L3">
-        <v>4.0793645231718543</v>
+        <v>3.0955757579027394</v>
       </c>
       <c r="M3">
-        <v>47.52686628211962</v>
+        <v>43.528560084277878</v>
       </c>
       <c r="N3">
-        <v>1.2337912591205311</v>
+        <v>0.86847484869280922</v>
       </c>
       <c r="O3">
-        <v>10.013314752105011</v>
+        <v>7.6960665910163755</v>
       </c>
       <c r="P3">
-        <v>2.0396822615859271</v>
+        <v>1.5477878789513697</v>
       </c>
       <c r="Q3">
-        <v>23.76343314105981</v>
+        <v>21.764280042138939</v>
       </c>
       <c r="R3">
-        <v>17.412308621236757</v>
+        <v>17.538886593443596</v>
       </c>
       <c r="S3">
-        <v>53.053599776247644</v>
+        <v>52.73550471407988</v>
       </c>
       <c r="T3">
-        <v>991.61918051190457</v>
+        <v>1306.643417304718</v>
       </c>
       <c r="U3">
-        <v>33.608848569225145</v>
+        <v>36.524998162202778</v>
       </c>
       <c r="V3">
         <v>0.91416402296412058</v>
@@ -3003,25 +3003,25 @@
         <v>1.0520403398712741</v>
       </c>
       <c r="X3">
-        <v>0.38650392442366588</v>
+        <v>0.3729967042319709</v>
       </c>
       <c r="Y3">
-        <v>0.65607148345786714</v>
+        <v>0.59251004765122339</v>
       </c>
       <c r="Z3">
-        <v>0.12666568974613379</v>
+        <v>0.14042828566942955</v>
       </c>
       <c r="AA3">
-        <v>0.11433596981299933</v>
+        <v>0.13018953196318553</v>
       </c>
       <c r="AB3">
-        <v>7.7031546993753626</v>
+        <v>6.616426318535531</v>
       </c>
       <c r="AC3">
-        <v>11.638053180583652</v>
+        <v>10.095432176332205</v>
       </c>
       <c r="AD3">
-        <v>70.644521397067592</v>
+        <v>67.355804134320536</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -3029,10 +3029,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C4">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="D4">
         <v>63.625211551169748</v>
@@ -3041,16 +3041,16 @@
         <v>26.856762260043379</v>
       </c>
       <c r="F4">
-        <v>40.817407352328708</v>
+        <v>29.359889499043451</v>
       </c>
       <c r="G4">
-        <v>16.907916642784247</v>
+        <v>9.6335804127491631</v>
       </c>
       <c r="H4">
-        <v>1.3969410159964397</v>
+        <v>2.9176984856535872</v>
       </c>
       <c r="I4">
-        <v>-1.0289663671388842</v>
+        <v>1.9695692331848147</v>
       </c>
       <c r="J4">
         <v>0.37114746822000777</v>
@@ -3059,34 +3059,34 @@
         <v>0.26459254944038024</v>
       </c>
       <c r="L4">
-        <v>6.2964151659509495</v>
+        <v>3.8828572555931076</v>
       </c>
       <c r="M4">
-        <v>52.2582501720415</v>
+        <v>45.498747927928385</v>
       </c>
       <c r="N4">
-        <v>1.871750452659805</v>
+        <v>0.9789500119591098</v>
       </c>
       <c r="O4">
-        <v>10.971113200739046</v>
+        <v>7.2101465569496286</v>
       </c>
       <c r="P4">
-        <v>3.1482075829754748</v>
+        <v>1.9414286277965538</v>
       </c>
       <c r="Q4">
-        <v>26.12912508602075</v>
+        <v>22.749373963964192</v>
       </c>
       <c r="R4">
-        <v>18.149808759680454</v>
+        <v>18.463787274158676</v>
       </c>
       <c r="S4">
-        <v>55.148071890782667</v>
+        <v>54.766856369049812</v>
       </c>
       <c r="T4">
-        <v>579.26470732441351</v>
+        <v>939.03883987695679</v>
       </c>
       <c r="U4">
-        <v>30.49163284750788</v>
+        <v>34.725498805318352</v>
       </c>
       <c r="V4">
         <v>0.96802813621256734</v>
@@ -3095,25 +3095,25 @@
         <v>0.97316342672652845</v>
       </c>
       <c r="X4">
-        <v>0.42004234432962162</v>
+        <v>0.39066297709515174</v>
       </c>
       <c r="Y4">
-        <v>0.71434636338578</v>
+        <v>0.617668239847117</v>
       </c>
       <c r="Z4">
-        <v>0.13701888645024943</v>
+        <v>0.17162290395130861</v>
       </c>
       <c r="AA4">
-        <v>0.13715911651478205</v>
+        <v>0.17340748826671137</v>
       </c>
       <c r="AB4">
-        <v>9.98829062437737</v>
+        <v>7.28108287133355</v>
       </c>
       <c r="AC4">
-        <v>9.5132628857617938</v>
+        <v>7.3122964200515</v>
       </c>
       <c r="AD4">
-        <v>74.147082257356644</v>
+        <v>67.57832571408882</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -3121,10 +3121,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>266</v>
       </c>
       <c r="D5">
         <v>56.390888454930227</v>
@@ -3133,16 +3133,16 @@
         <v>25.643658689885338</v>
       </c>
       <c r="F5">
-        <v>34.800905094717855</v>
+        <v>20.704335942427075</v>
       </c>
       <c r="G5">
-        <v>16.098887611694106</v>
+        <v>6.0522133878549287</v>
       </c>
       <c r="H5">
-        <v>1.550964213534876</v>
+        <v>4.3090675078564944</v>
       </c>
       <c r="I5">
-        <v>-1.0177902802337124</v>
+        <v>5.5926778545783229</v>
       </c>
       <c r="J5">
         <v>0.37079134592998025</v>
@@ -3151,34 +3151,34 @@
         <v>0.2656416322952781</v>
       </c>
       <c r="L5">
-        <v>7.1348029152765955</v>
+        <v>2.9644720113751206</v>
       </c>
       <c r="M5">
-        <v>59.604683851249483</v>
+        <v>46.442263593415554</v>
       </c>
       <c r="N5">
-        <v>2.0782719282127489</v>
+        <v>0.66604431863289271</v>
       </c>
       <c r="O5">
-        <v>12.5453987372123</v>
+        <v>5.9934466141904084</v>
       </c>
       <c r="P5">
-        <v>3.5674014576382977</v>
+        <v>1.4822360056875603</v>
       </c>
       <c r="Q5">
-        <v>29.802341925624741</v>
+        <v>23.221131796707777</v>
       </c>
       <c r="R5">
-        <v>18.115197505584327</v>
+        <v>18.788135347955208</v>
       </c>
       <c r="S5">
-        <v>56.124213195138658</v>
+        <v>56.153471201033732</v>
       </c>
       <c r="T5">
-        <v>453.13773269936405</v>
+        <v>1090.0154613522745</v>
       </c>
       <c r="U5">
-        <v>25.797959903438407</v>
+        <v>32.519531298981306</v>
       </c>
       <c r="V5">
         <v>0.96374248262138207</v>
@@ -3187,25 +3187,25 @@
         <v>0.96371207021506655</v>
       </c>
       <c r="X5">
-        <v>0.46690166214183115</v>
+        <v>0.42117502972134729</v>
       </c>
       <c r="Y5">
-        <v>0.76926670740655989</v>
+        <v>0.62312898208658452</v>
       </c>
       <c r="Z5">
-        <v>0.16716744572953926</v>
+        <v>0.23828473086597243</v>
       </c>
       <c r="AA5">
-        <v>0.16473530177229154</v>
+        <v>0.269391324912734</v>
       </c>
       <c r="AB5">
-        <v>8.8318779249006667</v>
+        <v>5.1456323365301024</v>
       </c>
       <c r="AC5">
-        <v>8.2065893990334491</v>
+        <v>4.5825233740934168</v>
       </c>
       <c r="AD5">
-        <v>71.27436424088269</v>
+        <v>58.0156538634991</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -3213,10 +3213,10 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>272</v>
       </c>
       <c r="D6">
         <v>51.519001940317587</v>
@@ -3225,16 +3225,16 @@
         <v>24.85774488399155</v>
       </c>
       <c r="F6">
-        <v>32.391287475976263</v>
+        <v>18.243368808308471</v>
       </c>
       <c r="G6">
-        <v>15.672855218341098</v>
+        <v>5.7620791243901106</v>
       </c>
       <c r="H6">
-        <v>1.4763008786334775</v>
+        <v>4.5599627845125</v>
       </c>
       <c r="I6">
-        <v>-1.0349048501861562</v>
+        <v>5.7850588074936526</v>
       </c>
       <c r="J6">
         <v>0.37175557556825906</v>
@@ -3243,34 +3243,34 @@
         <v>0.26521478843913149</v>
       </c>
       <c r="L6">
-        <v>7.3414036423076636</v>
+        <v>2.6884304894833031</v>
       </c>
       <c r="M6">
-        <v>60.521077637223883</v>
+        <v>46.95106217339336</v>
       </c>
       <c r="N6">
-        <v>2.16404844344521</v>
+        <v>0.59473719649987078</v>
       </c>
       <c r="O6">
-        <v>12.745227349565916</v>
+        <v>5.9951755434151979</v>
       </c>
       <c r="P6">
-        <v>3.6707018211538318</v>
+        <v>1.3442152447416516</v>
       </c>
       <c r="Q6">
-        <v>30.260538818611941</v>
+        <v>23.47553108669668</v>
       </c>
       <c r="R6">
-        <v>17.615558838161864</v>
+        <v>18.372734167628707</v>
       </c>
       <c r="S6">
-        <v>55.050785807854233</v>
+        <v>55.085741733618775</v>
       </c>
       <c r="T6">
-        <v>402.35379295063547</v>
+        <v>1098.0727208503467</v>
       </c>
       <c r="U6">
-        <v>24.663746762419546</v>
+        <v>31.200305937038049</v>
       </c>
       <c r="V6">
         <v>0.96608699365910289</v>
@@ -3279,25 +3279,25 @@
         <v>0.96586889811156607</v>
       </c>
       <c r="X6">
-        <v>0.4811021379808923</v>
+        <v>0.42963635867887517</v>
       </c>
       <c r="Y6">
-        <v>0.80023143870287161</v>
+        <v>0.64741071086221658</v>
       </c>
       <c r="Z6">
-        <v>0.17693648540964149</v>
+        <v>0.26084609417564864</v>
       </c>
       <c r="AA6">
-        <v>0.18053837427853628</v>
+        <v>0.2979301540388552</v>
       </c>
       <c r="AB6">
-        <v>8.73665002893438</v>
+        <v>4.75065854108982</v>
       </c>
       <c r="AC6">
-        <v>7.6654943851402679</v>
+        <v>4.1776285942923943</v>
       </c>
       <c r="AD6">
-        <v>70.324533556329257</v>
+        <v>55.315101631297914</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -3305,10 +3305,10 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="C7">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="D7">
         <v>47.962027906230006</v>
@@ -3317,16 +3317,16 @@
         <v>24.767804468397294</v>
       </c>
       <c r="F7">
-        <v>30.3807293490823</v>
+        <v>16.660399965625775</v>
       </c>
       <c r="G7">
-        <v>15.647500339991314</v>
+        <v>4.6751677845096005</v>
       </c>
       <c r="H7">
-        <v>1.4467475710617506</v>
+        <v>4.6970102766420165</v>
       </c>
       <c r="I7">
-        <v>-1.0428496676404224</v>
+        <v>8.2443398878973611</v>
       </c>
       <c r="J7">
         <v>0.37263863986685208</v>
@@ -3335,34 +3335,34 @@
         <v>0.26795966143684</v>
       </c>
       <c r="L7">
-        <v>7.5799416930804924</v>
+        <v>2.6674852792532495</v>
       </c>
       <c r="M7">
-        <v>62.811673433145067</v>
+        <v>45.436209296483106</v>
       </c>
       <c r="N7">
-        <v>2.2480402361396141</v>
+        <v>0.58584652789263747</v>
       </c>
       <c r="O7">
-        <v>13.377917521104605</v>
+        <v>5.2896429399804292</v>
       </c>
       <c r="P7">
-        <v>3.7899708465402462</v>
+        <v>1.3337426396266248</v>
       </c>
       <c r="Q7">
-        <v>31.405836716572534</v>
+        <v>22.718104648241553</v>
       </c>
       <c r="R7">
-        <v>17.138749456173347</v>
+        <v>17.932783954839991</v>
       </c>
       <c r="S7">
-        <v>54.605335477742663</v>
+        <v>55.204792964949469</v>
       </c>
       <c r="T7">
-        <v>362.80315865199714</v>
+        <v>1030.2849629656128</v>
       </c>
       <c r="U7">
-        <v>23.765080606187372</v>
+        <v>32.066238675075972</v>
       </c>
       <c r="V7">
         <v>0.96734921344687119</v>
@@ -3371,25 +3371,25 @@
         <v>0.96700424992385381</v>
       </c>
       <c r="X7">
-        <v>0.50014187052472</v>
+        <v>0.44458283445094915</v>
       </c>
       <c r="Y7">
-        <v>0.8250150742475626</v>
+        <v>0.65329232218261035</v>
       </c>
       <c r="Z7">
-        <v>0.19244967849540073</v>
+        <v>0.28699536893331523</v>
       </c>
       <c r="AA7">
-        <v>0.19598235150757448</v>
+        <v>0.37628110067765014</v>
       </c>
       <c r="AB7">
-        <v>8.40920696353469</v>
+        <v>4.3861723494441236</v>
       </c>
       <c r="AC7">
-        <v>7.2148567773334653</v>
+        <v>3.1460698829434435</v>
       </c>
       <c r="AD7">
-        <v>68.848806168161019</v>
+        <v>51.019465571679255</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -3397,10 +3397,10 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C8">
-        <v>96</v>
+        <v>536</v>
       </c>
       <c r="D8">
         <v>45.237575165070282</v>
@@ -3409,16 +3409,16 @@
         <v>25.229876942897306</v>
       </c>
       <c r="F8">
-        <v>28.666168178601591</v>
+        <v>16.336633478127791</v>
       </c>
       <c r="G8">
-        <v>15.696765845432573</v>
+        <v>2.8113610469431478</v>
       </c>
       <c r="H8">
-        <v>1.4452059727011868</v>
+        <v>4.4227199143624585</v>
       </c>
       <c r="I8">
-        <v>-0.98167590837849772</v>
+        <v>17.435642844886718</v>
       </c>
       <c r="J8">
         <v>0.37400760534579036</v>
@@ -3427,34 +3427,34 @@
         <v>0.2803285227766843</v>
       </c>
       <c r="L8">
-        <v>7.325066409718759</v>
+        <v>2.7948577528196856</v>
       </c>
       <c r="M8">
-        <v>62.765725120490266</v>
+        <v>33.6157220562471</v>
       </c>
       <c r="N8">
-        <v>2.1808568681125933</v>
+        <v>0.62816215287479094</v>
       </c>
       <c r="O8">
-        <v>13.878334881755054</v>
+        <v>3.1456505707771014</v>
       </c>
       <c r="P8">
-        <v>3.6625332048593795</v>
+        <v>1.3974288764098428</v>
       </c>
       <c r="Q8">
-        <v>31.382862560245133</v>
+        <v>16.807861028123551</v>
       </c>
       <c r="R8">
-        <v>16.51452099035804</v>
+        <v>17.226930603569773</v>
       </c>
       <c r="S8">
-        <v>53.453822216359988</v>
+        <v>57.296139437503626</v>
       </c>
       <c r="T8">
-        <v>354.08390961070791</v>
+        <v>927.48159330329588</v>
       </c>
       <c r="U8">
-        <v>24.224357419958242</v>
+        <v>43.625679622585807</v>
       </c>
       <c r="V8">
         <v>0.96841018460180273</v>
@@ -3463,25 +3463,25 @@
         <v>0.96795122424828028</v>
       </c>
       <c r="X8">
-        <v>0.50385953366207348</v>
+        <v>0.45062233362437915</v>
       </c>
       <c r="Y8">
-        <v>0.81207012856533367</v>
+        <v>0.62257315973449157</v>
       </c>
       <c r="Z8">
-        <v>0.20213849169470516</v>
+        <v>0.29249792741067354</v>
       </c>
       <c r="AA8">
-        <v>0.19985074046807347</v>
+        <v>0.59900331645026317</v>
       </c>
       <c r="AB8">
-        <v>8.20617304989361</v>
+        <v>4.4450470503282435</v>
       </c>
       <c r="AC8">
-        <v>7.1554840102552051</v>
+        <v>1.4529106491880997</v>
       </c>
       <c r="AD8">
-        <v>67.77748640887873</v>
+        <v>43.702700271393432</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -3489,10 +3489,10 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C9">
-        <v>90</v>
+        <v>428</v>
       </c>
       <c r="D9">
         <v>43.446264664276391</v>
@@ -3501,16 +3501,16 @@
         <v>26.591727303779724</v>
       </c>
       <c r="F9">
-        <v>25.364384600584554</v>
+        <v>21.688386832383895</v>
       </c>
       <c r="G9">
-        <v>16.534040149093979</v>
+        <v>3.4767841435010705</v>
       </c>
       <c r="H9">
-        <v>1.7822115880622542</v>
+        <v>2.5080101623100939</v>
       </c>
       <c r="I9">
-        <v>-0.97924538346471912</v>
+        <v>14.120921954190004</v>
       </c>
       <c r="J9">
         <v>0.37649886199754568</v>
@@ -3519,34 +3519,34 @@
         <v>0.29014733557735956</v>
       </c>
       <c r="L9">
-        <v>5.4173989998351155</v>
+        <v>4.2686784629630043</v>
       </c>
       <c r="M9">
-        <v>54.850440854959217</v>
+        <v>30.389382709392002</v>
       </c>
       <c r="N9">
-        <v>1.5584412474668046</v>
+        <v>1.1355192848425326</v>
       </c>
       <c r="O9">
-        <v>12.549167873807201</v>
+        <v>3.18827706589472</v>
       </c>
       <c r="P9">
-        <v>2.7086994999175578</v>
+        <v>2.1343392314815022</v>
       </c>
       <c r="Q9">
-        <v>27.425220427479609</v>
+        <v>15.194691354696001</v>
       </c>
       <c r="R9">
-        <v>15.600310748776439</v>
+        <v>15.751749054588224</v>
       </c>
       <c r="S9">
-        <v>49.228784496098463</v>
+        <v>52.098422760969584</v>
       </c>
       <c r="T9">
-        <v>459.66987109298213</v>
+        <v>583.2867075657872</v>
       </c>
       <c r="U9">
-        <v>28.866992579644617</v>
+        <v>50.72825466201224</v>
       </c>
       <c r="V9">
         <v>0.9697562157220061</v>
@@ -3555,25 +3555,25 @@
         <v>0.96918262734228977</v>
       </c>
       <c r="X9">
-        <v>0.45687104277662338</v>
+        <v>0.4416229879006292</v>
       </c>
       <c r="Y9">
-        <v>0.78537984411856221</v>
+        <v>0.61237804765280923</v>
       </c>
       <c r="Z9">
-        <v>0.19838751118886683</v>
+        <v>0.21958272495018619</v>
       </c>
       <c r="AA9">
-        <v>0.19251669047671874</v>
+        <v>0.51528162447466863</v>
       </c>
       <c r="AB9">
-        <v>7.9558166117848916</v>
+        <v>6.7865960384463619</v>
       </c>
       <c r="AC9">
-        <v>7.4102247314217706</v>
+        <v>1.8471149523987072</v>
       </c>
       <c r="AD9">
-        <v>66.713164127816</v>
+        <v>53.56009459250415</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -3581,10 +3581,10 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="D10">
         <v>42.690439915239153</v>
@@ -3593,16 +3593,16 @@
         <v>29.023880380551287</v>
       </c>
       <c r="F10">
-        <v>26.927142189095829</v>
+        <v>27.943260762269251</v>
       </c>
       <c r="G10">
-        <v>17.990893403072761</v>
+        <v>4.0752852459999067</v>
       </c>
       <c r="H10">
-        <v>1.4635138047184493</v>
+        <v>1.3193860300014153</v>
       </c>
       <c r="I10">
-        <v>-0.96686505079367757</v>
+        <v>12.804815263569376</v>
       </c>
       <c r="J10">
         <v>0.37868769132331831</v>
@@ -3611,34 +3611,34 @@
         <v>0.2980036878849982</v>
       </c>
       <c r="L10">
-        <v>4.93913045013802</v>
+        <v>5.186953136397622</v>
       </c>
       <c r="M10">
-        <v>48.954478887949065</v>
+        <v>26.675747667406156</v>
       </c>
       <c r="N10">
-        <v>1.4854618503370782</v>
+        <v>1.5891567618796465</v>
       </c>
       <c r="O10">
-        <v>11.48583830283393</v>
+        <v>2.9787873966540781</v>
       </c>
       <c r="P10">
-        <v>2.46956522506901</v>
+        <v>2.593476568198811</v>
       </c>
       <c r="Q10">
-        <v>24.477239443974533</v>
+        <v>13.337873833703078</v>
       </c>
       <c r="R10">
-        <v>14.672050963608928</v>
+        <v>14.651834532021693</v>
       </c>
       <c r="S10">
-        <v>45.796636828755645</v>
+        <v>48.42895153284725</v>
       </c>
       <c r="T10">
-        <v>495.37860429787855</v>
+        <v>471.72539013211224</v>
       </c>
       <c r="U10">
-        <v>35.024930770430807</v>
+        <v>62.905859349765556</v>
       </c>
       <c r="V10">
         <v>0.97020586529407171</v>
@@ -3647,25 +3647,25 @@
         <v>0.96953741227665191</v>
       </c>
       <c r="X10">
-        <v>0.43651327876233492</v>
+        <v>0.44052909463223322</v>
       </c>
       <c r="Y10">
-        <v>0.766396731410675</v>
+        <v>0.604034775935174</v>
       </c>
       <c r="Z10">
-        <v>0.18221258301596385</v>
+        <v>0.17814457459400784</v>
       </c>
       <c r="AA10">
-        <v>0.18985844619444392</v>
+        <v>0.48643266695827003</v>
       </c>
       <c r="AB10">
-        <v>8.67250539486555</v>
+        <v>8.9702735531118289</v>
       </c>
       <c r="AC10">
-        <v>7.5280035166829888</v>
+        <v>1.9950672636587059</v>
       </c>
       <c r="AD10">
-        <v>67.546693008063286</v>
+        <v>58.572738626345441</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -3673,10 +3673,10 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C11">
-        <v>74</v>
+        <v>242</v>
       </c>
       <c r="D11">
         <v>42.246156795643429</v>
@@ -3685,16 +3685,16 @@
         <v>31.745261925590011</v>
       </c>
       <c r="F11">
-        <v>26.685266714470291</v>
+        <v>29.952850393793184</v>
       </c>
       <c r="G11">
-        <v>19.707436989084709</v>
+        <v>6.0262410627779683</v>
       </c>
       <c r="H11">
-        <v>1.4578166154074002</v>
+        <v>1.0260548028175021</v>
       </c>
       <c r="I11">
-        <v>-0.97293372761097063</v>
+        <v>8.16959510700196</v>
       </c>
       <c r="J11">
         <v>0.37976698703487</v>
@@ -3703,34 +3703,34 @@
         <v>0.2974901398093604</v>
       </c>
       <c r="L11">
-        <v>4.799241496337511</v>
+        <v>5.5605878492801128</v>
       </c>
       <c r="M11">
-        <v>45.969229487816925</v>
+        <v>29.93130250739431</v>
       </c>
       <c r="N11">
-        <v>1.4485449743826555</v>
+        <v>1.7781295147353609</v>
       </c>
       <c r="O11">
-        <v>10.774953786253906</v>
+        <v>3.8795556404442246</v>
       </c>
       <c r="P11">
-        <v>2.3996207481687555</v>
+        <v>2.7802939246400564</v>
       </c>
       <c r="Q11">
-        <v>22.984614743908462</v>
+        <v>14.965651253697155</v>
       </c>
       <c r="R11">
-        <v>14.165430708778912</v>
+        <v>14.114342072660316</v>
       </c>
       <c r="S11">
-        <v>44.045269137665265</v>
+        <v>45.168834482066885</v>
       </c>
       <c r="T11">
-        <v>504.50352397952679</v>
+        <v>435.47134737755295</v>
       </c>
       <c r="U11">
-        <v>40.648614309478759</v>
+        <v>61.464666314980533</v>
       </c>
       <c r="V11">
         <v>0.99360462702951247</v>
@@ -3739,25 +3739,25 @@
         <v>0.99366900342747122</v>
       </c>
       <c r="X11">
-        <v>0.42108351440146852</v>
+        <v>0.43367843645727311</v>
       </c>
       <c r="Y11">
-        <v>0.76212240580287038</v>
+        <v>0.61603925316700014</v>
       </c>
       <c r="Z11">
-        <v>0.17814155597142548</v>
+        <v>0.16604412501378138</v>
       </c>
       <c r="AA11">
-        <v>0.18645023673786507</v>
+        <v>0.3741093242230395</v>
       </c>
       <c r="AB11">
-        <v>9.6521336467309915</v>
+        <v>10.689642548678116</v>
       </c>
       <c r="AC11">
-        <v>7.8405733949230427</v>
+        <v>3.121401818263696</v>
       </c>
       <c r="AD11">
-        <v>68.821384453615224</v>
+        <v>64.532529542278624</v>
       </c>
     </row>
   </sheetData>
